--- a/results/exp_F_improvements.xlsx
+++ b/results/exp_F_improvements.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5542761087417603</v>
+        <v>0.5862144827842712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5804477334022522</v>
+        <v>0.5862144827842712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5243297219276428</v>
+        <v>0.5984967947006226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5889051556587219</v>
+        <v>0.5516940951347351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.645361602306366</v>
+        <v>0.5870553851127625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5764639973640442</v>
+        <v>0.5363831520080566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5903816819190979</v>
+        <v>0.5674307942390442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6714558601379395</v>
+        <v>0.5674307942390442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5547864437103271</v>
+        <v>0.556399941444397</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5648937225341797</v>
+        <v>0.5828758478164673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6686012148857117</v>
+        <v>0.6416516900062561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.580275297164917</v>
+        <v>0.5345180630683899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.592900812625885</v>
+        <v>0.5507810115814209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6015911102294922</v>
+        <v>0.5507810115814209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5090205073356628</v>
+        <v>0.5735965371131897</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5560581684112549</v>
+        <v>0.5509580969810486</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6120508909225464</v>
+        <v>0.5537263751029968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6320258378982544</v>
+        <v>0.5537824034690857</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.5831253528594971</v>
+        <v>0.5601266622543335</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.5995261073112488</v>
+        <v>0.5601266622543335</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6393423676490784</v>
+        <v>0.5725563764572144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.5501260757446289</v>
+        <v>0.5544628500938416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.5301691293716431</v>
+        <v>0.5241734385490417</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.5237976312637329</v>
+        <v>0.5834402441978455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6244875192642212</v>
+        <v>0.6120653748512268</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.5510895252227783</v>
+        <v>0.6120653748512268</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.5437495708465576</v>
+        <v>0.524216890335083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.5767802000045776</v>
+        <v>0.5409384965896606</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.7773632407188416</v>
+        <v>0.753476083278656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.5499223470687866</v>
+        <v>0.6693509817123413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.6293213367462158</v>
+        <v>0.5969101786613464</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.5371294021606445</v>
+        <v>0.5969101786613464</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.5467275381088257</v>
+        <v>0.5773798823356628</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.5717369914054871</v>
+        <v>0.5302903652191162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.6201103329658508</v>
+        <v>0.6154826879501343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.5527039766311646</v>
+        <v>0.5817859768867493</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
